--- a/education_forms/046_open_access_courseware_distribution_request_form--education_forms.xlsx
+++ b/education_forms/046_open_access_courseware_distribution_request_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Date Of Request Day</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Date Of Request Month</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Date Of Request Year</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'student'},_'student',_'student',_'student']}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Student'}, 'Student', 'Student', 'Student']}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'faculty'},_'faculty',_'faculty',_'faculty']}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Faculty'}, 'Faculty', 'Faculty', 'Faculty']}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'staff'},_'staff',_'staff',_'staff']}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Staff'}, 'Staff', 'Staff', 'Staff']}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'department_1'},_'department_1',_'department_1',_'department_1',_'department_1']}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Department 1'}, 'Department 1', 'Department 1', 'Department 1', 'Department 1']}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'department_2'},_'department_2',_'department_2',_'department_2',_'department_2']}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Department 2'}, 'Department 2', 'Department 2', 'Department 2', 'Department 2']}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'course_material'},_'course_material',_'course_material',_'course_material']}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Course Material'}, 'Course Material', 'Course Material', 'Course Material']}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'courseware'},_'courseware',_'courseware',_'courseware']}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Courseware'}, 'Courseware', 'Courseware', 'Courseware']}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'other'},_'other',_'other',_'other']}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Other'}, 'Other', 'Other', 'Other']}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'self_use'},_'self_use',_'self_use',_'self_use',_'self_use']}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Self Use'}, 'Self Use', 'Self Use', 'Self Use', 'Self Use']}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'options':_[{'name':_'teaching_and_learning'},_'teaching_and_learning',_'teaching_and_learning',_'teaching_and_learning',_'teaching_and_learning']}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'options': [{'name': 'Teaching and Learning'}, 'Teaching and Learning', 'Teaching and Learning', 'Teaching and Learning', 'Teaching and Learning']}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
